--- a/docs/triton-learning/cards/triton-lesson-10-block-scaled-matmul-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-10-block-scaled-matmul-technical-qa.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -43,8 +43,8 @@
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：乘一个 scale 只是把所有数在 log₂ 轴上一起平移，窗口宽度由元素格式决定：E2M1 只有约 3.58 档，E4M3 约 17.8 档。
 • [T#B#整张量 scale]：整张量只能平移一次，比最大值小超过窗口宽度的数就掉出窗口，变成 0 或只剩最小值；一个离群值把 scale 拉大，每一块都受害。
-• [T#B#块 scale]：每块各自平移，窗口只需盖住块内的跨度，离群值只坏它所在的那一块。例：64 个数里有一个 12，MXFP4 每块一个 scale 时 23 个非零数变 0，整行一个 scale 时变 0 的有 42 个。
-• [T#B#FP8]：12 到 0.01 约 10 档，E4M3 一个 scale 就装得下：同一个例子整行只用一个 scale，也没有数变 0。
+• [T#B#块 scale]：每块各自平移，窗口只需盖住块内的跨度，离群值只坏它所在的那一块：整行共用一个 scale 时，远离离群值的整块小数都会掉出窗口；每块一个 scale 时，受害的只有含离群值的那一块。
+• [T#B#FP8]：E4M3 的窗口约 17.8 档：一组从 0.01 到 12 的数跨 log₂(12 ÷ 0.01) ≈ 10.2 档，一个整张量 scale 就装得下；同一组数放进 E2M1 的 3.58 档就装不下。
 [T#B,!c47f17#边界]：块缩放对 FP4 是必需，对 FP8 是改善；块越小越贴合局部范围，但 scale 要存的、要搬的、要乘的都越多。</t>
         </is>
       </c>
@@ -62,21 +62,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MXFP4 和 NVFP4 的元素都是 E2M1。两者的块大小、块 scale 的类型、每个数平均占几位、块最大值能否对准 E2M1 的最大值 6、量化要读几趟数据各是怎样？各自的代价在哪里？</t>
+          <t xml:space="preserve">MXFP4 和 NVFP4 的元素都是 E2M1：MXFP4 每 32 个元素配一个 E8M0 块 scale（只能是 2 的幂），每个数平均 4.25 位；NVFP4 每 16 个元素配一个 E4M3 块 scale，外加每张量一个 FP32 scale，每个数平均 4.5 位。这两种块 scale 类型各带来什么好处、付出什么代价？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：MXFP4 每 32 个元素一个 E8M0 scale（只能是 2 的幂），每个数 4.25 位；NVFP4 每 16 个元素一个 E4M3 scale，再加每张量一个 FP32 scale，每个数 4.5 位。
-• [T#B#MXFP4]：E8M0 只能整档移动，块最大值一般对不准 6：按 OCP 规则向下取会截断（尾数大于 1.5 时最大值饱和），向上取则浪费顶端格点、更多小数变 0；E8M0 有 254 档，各块互不影响。
-• [T#B#NVFP4]：E4M3 的 3 位尾数能把块最大值对到 6 附近，块更小，一个离群值只连累 15 个数；但 E4M3 只有约 17.8 档，要靠每张量的 FP32 scale 定位窗口，量化前得先求整张量 amax，多一趟显存往返。
-• [T#B#硬件]：MX 是 OCP 标准，NVIDIA Blackwell 与 AMD CDNA4 原生支持；NVFP4 由 NVIDIA 提出，Blackwell 原生支持。
-[T#B,!c47f17#边界]：每张量 scale 只平移 E4M3 的窗口、不加宽；块与块的 amax 相差超过约 17.8 档时，NVFP4 的小块会出问题。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：MXFP4 的 E8M0 scale 范围宽、各块互不影响，但只能整档移动，对不准 E2M1 的最大值 6；NVFP4 的 E4M3 scale 能对准 6，但窗口窄，要靠每张量的 FP32 scale 定位，量化还要多读一趟。
+• [T#B#MXFP4]：E8M0 有 254 档，每块各取各的 2 的幂，块与块的幅度差几十档也装得下；代价是块最大值缩放后一般落不到 6 上，顶端的格点要么用不满、要么被截断。
+• [T#B#NVFP4]：E4M3 的 3 位尾数能把块最大值细调到 6 附近，顶端格点用得满；块更小，一个离群值只连累 15 个数。代价是 E4M3 只有约 17.8 档：每张量 scale 只决定这个窗口放在哪，量化前得先求整张量的 amax，多一趟显存往返。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32·E8M0·4.25 位 对 16·E4M3+FP32·4.5 位；对不准 6 对多一趟</t>
+          <t xml:space="preserve">E8M0：范围宽、对不准 6；E4M3：对得准 6、窗口窄、多一趟</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -88,14 +86,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NVFP4 的两级 scale：每张量 s_enc = 6 × 448 / amax_张量；每块的 scale = amax_块 / 6 × s_enc，再舍入成 E4M3（最大 448，最小正数 2⁻⁹，约 17.8 档）。若一张激活张量各块的 amax 从 3×10⁴ 到 2×10⁻³，哪些块会出问题？每张量 scale 能不能解决？MXFP4 呢？</t>
+          <t xml:space="preserve">NVFP4 的两级 scale：每张量 s_enc = 6 × 448 / amax_张量；每块的 scale = amax_块 / 6 × s_enc，再舍入成 E4M3（最大 448，最小正数 2⁻⁹，约 17.8 档）。若一张激活张量各块的 amax 从 3×10⁴ 到 2×10⁻³，哪些块会出问题？为什么每张量 scale 解决不了？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：每张量 scale 只决定 E4M3 那 17.8 档的窗口放在哪里，不能把窗口变宽；各块的 scale 相差 log₂(1.5×10⁷) ≈ 23.8 档，装不进去。
 • [T#B#后果]：s_enc 把最大那块的 scale 对到 448；比它小 14.8 到 18.8 档的块，scale 落进次正规数、精度变差；更小的块 scale 舍成 0，整块变 0，对这个 0 求倒数还会得到 inf 或 NaN。
-• [T#B#MXFP4]：E8M0 有 254 档，每块各取各的 2 的幂，最小那块的 scale 是 2⁻¹¹，没有这个问题。
+• [T#B#对照 MXFP4]：E8M0 有 254 档，每块各取各的 2 的幂，最小那块的 scale 是 2⁻¹¹，没有这个问题。
 • [T#B#修法]：把第二级 scale 做细，比如每个 token（每行）一个 FP32；或者这张张量改用 MXFP4、FP8 或 BF16。
 [T#B,!c47f17#边界]：E2M1 本身“最大和次大格点差 1.5 倍”的舍入误差每块都有，不是这里的问题；换元素格式（比如 E1M2）也救不了已经是 0 的 scale。</t>
         </is>
@@ -114,7 +112,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">vLLM 服务里，某一层的输入激活在线量化成 NVFP4，第二级 scale 由整个 batch 共用一个 FP32（s_enc = 6 × 448 / 整个 batch 的 amax），块 scale 存成 E4M3（最小正数 2⁻⁹）。平时各块 amax 在 0.01 到 10 之间。某次 batch 里混进一个异常 token，它有一块的 amax 是 10⁴：同一 batch 里有些 token 输出明显出错，有些没事，单独跑出错的 token 又正常。原因是什么？换成 MXFP4 会怎样？怎么修？</t>
+          <t xml:space="preserve">vLLM 服务里，某一层的输入激活在线量化成 NVFP4，第二级 scale 由整个 batch 共用一个 FP32（s_enc = 6 × 448 / 整个 batch 的 amax），块 scale 存成 E4M3（最小正数 2⁻⁹）。平时各块 amax 在 0.01 到 10 之间。某次 batch 里混进一个异常 token，它有一块的 amax 是 10⁴：同一 batch 里有些 token 输出明显出错，有些没事，单独跑出错的 token 又正常。为什么一个 token 的结果会取决于同一 batch 里还有谁？怎样修，代价是什么？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -122,7 +120,6 @@
           <t xml:space="preserve">[T#B,!36b59d#结论]：整个 batch 共用的第二级 scale 被异常 token 抬高，所有块的 scale 在 E4M3 窗口里一起上移，幅度小的块 scale 下溢。
 • [T#B#谁出错]：块 scale 小于 2⁻¹⁰（这里约是 amax 小于 0.022）的块整块变 0，0.022 到 0.35 的块精度变差；变 0 的单位是块，所以只有含这类块的 token 明显出错。
 • [T#B#单独跑]：没有异常 token，第二级 scale 不会被抬高；一个 token 的结果于是取决于同一 batch 里还有谁，线上很难排查。
-• [T#B#MXFP4]：每块各取各的 2 的幂 scale，别的块不受影响；异常值只拖累同块的数，但块是 32 个，比 NVFP4 的 16 个连累更多。
 • [T#B#修法]：第二级 scale 改成每个 token 一个：影响限制在异常 token 自己，量化一趟就能做完；代价只是每行多一个 FP32，矩阵乘结束后按行乘回去。
 [T#B,!c47f17#边界]：异常 token 自己的块 amax 从 0.01 到 10⁴，相差约 20 档，它自己的小块仍会变 0。</t>
         </is>
@@ -141,22 +138,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MXFP4 量化时，OCP 规则取块 scale X = 2^e，e = ⌊log₂(amax)⌋ − 2（amax 是块内最大绝对值）。为什么对 log₂(amax) 向下取整、再减 2？这样取的代价是什么？另一种取法“向上取整”X = 2^⌈log₂(amax ÷ 6)⌉ 换来了什么、丢掉了什么？</t>
+          <t xml:space="preserve">MXFP4 量化时，OCP 规则取块 scale X = 2^e，e = ⌊log₂(amax)⌋ − 2（amax 是块内最大绝对值）；Triton 3.7.1 的 triton_kernels 默认用向上取整 X = 2^⌈log₂(amax ÷ 6)⌉。OCP 为什么对 log₂(amax) 向下取整再减 2？和向上取整相比，两种取法各把误差留在哪里？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：向下取整得到 amax 的二进制指数，也就是不超过 amax 的最大 2 的幂；减 2 是因为 E2M1 能表示的最大 2 的幂是 4。这样块最大值缩放后落在最上面一档 \[4, 8)，其余的数离“≤ 0.25 就变 0”这条线最远。
-• [T#B#代价]：\[4, 8) 这一档只有 4 和 6：amax 的尾数大于 1.5 时最大值饱和成 6，误差最多约 25%，比如 7.99 存成 6。
+• [T#B#向下取的代价]：\[4, 8) 这一档只有 4 和 6：amax 的尾数大于 1.5 时最大值饱和成 6，误差最多约 25%，比如 7.99 存成 6。
 • [T#B#向上取整]：保证不截断，但这些块的每个数都多除一个 2，小值更容易变 0。例：一块 \[7.5, 3.0, 0.4\]，向下取存成 6、3、0.5；向上取还原成 8、3、0。
-• [T#B#实测与选择]：2²² 个随机数上两种取法的总误差相近，区别在误差落在谁身上；OCP 规定向下取，Triton 的 triton_kernels 默认向上取，NVIDIA 的 MXFP8 训练配方也改用向上取。
-• [T#B#实现]：⌊log₂⌋ 直接读 FP32 的指数位（bits &amp; 0x7F800000），不要用浮点 log2：float32 的 log2(7.9999995) 会得到 3.0，正确的 ⌊log₂⌋ 是 2。
+• [T#B#总误差]：2²² 个随机数上两种取法的总误差相近，区别在误差落在块最大值上还是小值上。
 [T#B,!c47f17#边界]：测试或对接其他实现时，先确认对方用哪种取法：尾数大于 1.5 的块上，两种取法的 scale 相差 2 倍。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">读指数位；最大值进 \[4, 8)；截断最大值 对 小数变 0</t>
+          <t xml:space="preserve">最大值进 \[4, 8)；向下取截断最大值，向上取让小数变 0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -168,16 +164,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">块缩放矩阵乘 C = A·B：A 的每行、B 的每列沿 K 每 V 个元素共用一个块 scale，另外可能有每张量（或每行、每列）的 scale。这两类 scale 各能放在计算的哪一步乘？DeepSeek-V3 在 Hopper 上把 scale 乘在部分和上，没有原生指令的硬件把 scale 乘在元素上，Blackwell 在指令内部乘，三种做法谁对？</t>
+          <t xml:space="preserve">块缩放矩阵乘 C = A·B：A 的每行、B 的每列沿 K 每 V 个元素共用一个块 scale，另外可能有每张量（或每行、每列）的 scale。一个 scale 能放在计算的哪一步乘，由什么决定？按这条规则，这两类 scale 各能放在哪？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：能放在哪一步，只看 scale 沿哪个下标变化：不随 k 变的 scale 可以提到整个 K 求和的外面，矩阵乘结束后每个输出乘一次；块 scale 只能提到块内求和的外面。
 • [T#B#公式]：C\[m,n\] = s^A·s^B·Σ_j (X^A\[m,j\]·X^B\[n,j\]·Σ_{k∈块 j} P^A\[m,k\]·P^B\[k,n\])：最外层共 M·N 次乘法，中间层每块乘一次，P 是低精度元素。
-• [T#B#三种位置]：块 scale 乘在元素上（解码成 bf16 再乘，Triton 无原生指令时的后备、AMD CDNA3 的模拟）、乘在每块的部分和上（DeepSeek-V3 在 Hopper 上每 128 个 K 取出部分和）、在 MMA 指令内部（Blackwell 的 tcgen05.mma、sm_120 的 mma.sync 块缩放、CDNA4 的 scaled MFMA），三者数学上等价。
+• [T#B#三种放法]：块 scale 因此有三种放法，数学上等价：乘在元素上（解码成 bf16 再乘，Triton 无原生指令时的后备、AMD CDNA3 的模拟）、乘在每块的部分和上（DeepSeek-V3 在 Hopper 上每 128 个 K 取出部分和）、在 MMA 指令内部乘（Blackwell 的 tcgen05.mma、sm_120 的块缩放 mma.sync、CDNA4 的 scaled MFMA）。
 • [T#B#怎样选]：由硬件决定：在哪里乘最便宜，乘积和累加能保留多少精度。
-[T#B,!c47f17#边界]：tl.dot_scaled 只算块 scale 这两层；不随 k 变的 scale（比如 NVFP4 的每张量 FP32）要在 kernel 的 epilogue 里自己乘。</t>
+[T#B,!c47f17#边界]：tl.dot_scaled 只处理块 scale 与元素这两层；不随 k 变的 scale（比如 NVFP4 的每张量 FP32）要在 kernel 的 epilogue 里自己乘。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -194,7 +190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">写块缩放矩阵乘 kernel 时，scale 的分块（沿 K 每 V 个元素一块，量化时就定了）与 kernel 的分块（BLOCK_M、BLOCK_N、BLOCK_K）必须怎样对齐？K 方向与 M、N 方向有什么不同？自己写 split-K 时要注意什么？</t>
+          <t xml:space="preserve">写块缩放矩阵乘 kernel 时，scale 的分块（沿 K 每 V 个元素一块，量化时就定了）与 kernel 的分块（BLOCK_M、BLOCK_N、BLOCK_K）必须怎样对齐？为什么 K 方向和 M、N 方向的要求不同？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -220,22 +216,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">H100（sm_90）有 FP8 张量核（wgmma 支持 E4M3，每条指令 K = 32），但没有块缩放指令，累加器在寄存器里；Triton 3.7.1 把 MXFP8 的 tl.dot_scaled 编成 bf16 矩阵乘，用不上 FP8 张量核。若一定要用上 FP8 张量核，scale 该放在哪一步？要满足什么条件、代价在哪？NVFP4 行不行？DeepGEMM 为什么每 128 个 K 才乘一次 scale、取 BLOCK_K = 128？</t>
+          <t xml:space="preserve">H100（sm_90）有 FP8 张量核（wgmma 支持 E4M3，每条指令 K = 32），但没有块缩放指令，累加器在寄存器里；Triton 3.7.1 把 MXFP8 的 tl.dot_scaled 编成 bf16 矩阵乘，用不上 FP8 张量核。若改成把 MXFP8（V = 32）的块 scale 乘在部分和上：每 V 个 K 先用 FP8 张量核算出部分和，再乘 sA·sB 加进总累加器。和乘在元素上相比，这样多付什么代价？DeepGEMM 为什么改成每 128 个 K 才乘一次 scale？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：scale 要挪到每个 scale 块的部分和上：每 V 个 K 先用 FP8 张量核算出部分和 P_j，再乘 sA·sB 加进总累加器；条件是 V ≥ 指令的 K。
-• [T#B#MXFP8]：V = 32 正好等于 wgmma 的 K = 32，可行。
-• [T#B#代价]：多出的乘法（128 × 256 的块、V = 32 时约是乘在元素上的 2.7 倍）、部分和与总累加器同时占寄存器（这个块 bf16 版本已用满 255 个）、异步 wgmma 每段都要等结果。
-• [T#B#NVFP4]：V = 16 小于 K = 32，一条指令的部分和横跨两个 scale 块，拆不开，行不通。
-• [T#B#每 128 个]：乘 scale 和等待都降到 V = 32 时的 1/4（乘法比约 0.67）；而且 H800 的 FP8 累加只保留约 14 位，每 128 个元素提升到 FP32 累加顺带修了精度。
-[T#B,!c47f17#边界]：换来的是 FP8 张量核约为 bf16 两倍的峰值；多出的乘法能否藏在 MMA 后面，要靠测量。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：代价有三项：乘 scale 的次数变多、部分和与总累加器同时占寄存器、每段都要等异步 wgmma 出结果；每 128 个 K 一组把乘 scale 和等待都降到 V = 32 时的 1/4，还顺带修了 FP8 累加的精度。
+• [T#B#乘几次]：一个 BM × BN 的输出块在一个 scale 块上：乘在部分和上，每个部分和乘一次，共 BM·BN 次；乘在元素上，每个输入元素乘一次，共 V·(BM + BN) 次。比值 BM·BN / (V·(BM + BN)) 在 128 × 256、V = 32 时约 2.7。
+• [T#B#摊到每次乘加]：乘在元素上每次乘加摊到 1/BM + 1/BN 次乘 scale（128 × 256 时约 1/85），乘在部分和上摊到 1/V 次，所以 V 大于约 85 时部分和更省；V = 128 时比值约 0.67。
+• [T#B#累加精度]：H800 的 FP8 累加只保留约 14 位，每 128 个元素把部分和提升到 FP32 累加，顺带修了精度；这和少乘 scale 一起，是 DeepGEMM 取 BLOCK_K = 128 的两个理由。
+[T#B,!c47f17#边界]：这里只数乘 scale 的次数：没算解码的成本，次数也不等于时间；多出的乘法能否藏在 MMA 后面，要靠测量。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">V ≥ 指令 K；2.7 倍乘法、两套累加器、等待；128 一组兼修精度</t>
+          <t xml:space="preserve">多乘 scale、两套累加器、每段等待；BM·BN 对 V·(BM + BN)；128 一组降到 1/4、兼修累加精度</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -247,15 +242,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 的块缩放教程在 sm_100（B200）上，把逻辑形状 \[M, K/V\] 的 scale 在主机端预排成 (M/128, K/V/4, 32, 4, 4)，kernel 第 220 行再用 reshape、trans、reshape 还原成 \[BLOCK_M, BLOCK_K/V\] 交给 tl.dot_scaled。为什么要这样排？那串 reshape、trans 为什么不搬数据？</t>
+          <t xml:space="preserve">Triton 3.7.1 的块缩放教程在 sm_100（B200）上，把逻辑形状 \[M, K/V\] 的 scale 在主机端预排成 (M/128, K/V/4, 32, 4, 4)；kernel 里再用 reshape(rep_m, rep_k, 32, 4, 4).trans(0, 3, 2, 1, 4).reshape(BLOCK_M, BLOCK_K // V) 还原成逻辑形状交给 tl.dot_scaled。为什么要这样预排？那串 reshape、trans 为什么不搬数据？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：块内的 (32, 4, 4) 就是 TMEM 要的字节顺序：一块 128 行 × 4 个 scale（512 字节）放成 32 个 lane × 4 列，第 m 行在 lane m % 32、第 m / 32 列，每个 32 位格子装同一行相邻 4 个 K 块的 scale。
 • [T#B#搬运]：TMA 把若干整块搬进 SMEM，一个线程发 tcgen05.cp .32x128b.warpx4，把每块原样拷进 TMEM；全程不经过寄存器，也不重排字节。
-• [T#B#外层]：kc（第几组 4 个 scale）放在块的紧外层、mb（第几个 128 行组）放最外层，一个 K 步要用的块就是连续的；TMA 的块每维不超过 256，所以每块 512 字节写成 2 × 256。
-• [T#B#第 220 行]：只换取址规则：编译器（UseShmemForScales）认出这串固定写法，改写成 SMEM 描述符上的 memdesc_reshape 和 memdesc_trans，不生成读写指令。
+• [T#B#外层]：kc（第几组 4 个 scale）放在块的紧外层、mb（第几个 128 行组）放最外层，一个 K 步要用的块就是连续的。
+• [T#B#reshape 与 trans]：只换取址规则：编译器（UseShmemForScales）认出这串固定写法，改写成 SMEM 描述符上的 memdesc_reshape 和 memdesc_trans，不生成读写指令。
 [T#B,!c47f17#边界]：这是模式匹配：换一种存法或写法匹配不上，就走通用路径（每个 warp 读进寄存器再 tcgen05.st），结果照样对但更慢；预排是快路径的前提，不是结果正确的前提。</t>
         </is>
       </c>
@@ -273,21 +268,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">在 sm_100 上把 A 的块 scale 按逻辑形状 \[M, K/V\] 行优先存（每个 scale 1 字节），建二维 TMA 描述符，每次搬的块是 \[BLOCK_M, BLOCK_K/V\]：NVFP4 为 \[128, 16\]，MXFP4 为 \[128, 8\]，MXFP8 为 \[128, 4\]，K = 8192。TMA 的三条规则“每维不超过 256 个元素”“最内维的字节数是 16 的倍数”“行距是 16 字节的倍数”各约束哪个形状？哪些格式建不起来？用 Triton 主机端的 TensorDescriptor 时，错误在哪一步暴露？</t>
+          <t xml:space="preserve">在 sm_100 上用 Triton 3.7.1 建二维 TMA 描述符：A 的块 scale 按逻辑形状 \[M, K/V\] 行优先存（每个 scale 1 字节），每次搬的块是 \[BLOCK_M, BLOCK_K/V\]：NVFP4 为 \[128, 16\]，MXFP4 为 \[128, 8\]，MXFP8 为 \[128, 4\]，K = 8192。TMA 的三条规则“每维不超过 256 个元素”“最内维的字节数是 16 的倍数”“行距是 16 字节的倍数”各约束哪个形状，哪些格式因此建不起来？用主机端的 TensorDescriptor 时，这个错误在哪一步暴露？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：前两条约束一次搬运的块（CUDA 文档叫 box），第三条约束整个张量；整个张量每维可以到 2³²，不受 256 的限制。
 • [T#B#结果]：块的最内维：NVFP4 是 16 字节，可以建；MXFP4 的 8 字节、MXFP8 的 4 字节违反 16 字节规则，建不起来。行距是 512 或 256 字节，都满足。
-• [T#B#何时报错]：编译和在 Python 端构造 TensorDescriptor 都能通过，要到启动 kernel、调用 cuTensorMapEncodeTiled 时才失败；在 kernel 里用 tl.make_tensor_descriptor 建描述符时，编译期就检查最后一维至少 16 字节。
+• [T#B#主机端]：块最内维不足 16 字节时，编译和在 Python 端构造 TensorDescriptor 都能通过；按 CUDA 文档，要到启动 kernel、调用 cuTensorMapEncodeTiled 时才被拒（未在 sm_100 上实测）。行距不是 16 字节的倍数时则不同，构造 TensorDescriptor 这一步就断言失败。
+• [T#B#kernel 内]：在 kernel 里用 tl.make_tensor_descriptor 建描述符时，编译期就检查最后一维至少 16 字节。
 • [T#B#转置存]：按 \[K/V, M\] 存、块取 \[BLOCK_K/V, 128\] 时，最内维是 128 字节，三种格式都能建；对 M 的要求只来自行距，M 是 16 的倍数即可。
 [T#B,!c47f17#边界]：教程的 5D 描述符，块是 \[1, rep_m, rep_k, 2, 256\]，三条都满足；这种布局本身还要求 M 是 128 的倍数。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">块对张量；最内维 ≥ 16 字节；主机端描述符启动时才报错</t>
+          <t xml:space="preserve">块对张量；最内维 ≥ 16 字节；主机端：最内维启动时才被拒，行距构造时就查</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -299,23 +295,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 把同一行 tl.dot_scaled（比如 MXFP4 × MXFP4，两侧都带 scale）编译到 B200（sm_100）、RTX 5090（sm_120）、RTX 4090（sm_89）、MI355X（gfx950，CDNA4）和 MI300X（gfx942，CDNA3），各落成什么指令？scale 放在哪里？代价或限制在哪里？</t>
+          <t xml:space="preserve">Triton 3.7.1 编译同一行 tl.dot_scaled（MXFP4 × MXFP4，两侧都带 scale）时，按什么规则决定走原生块缩放指令、走软件换算还是编译失败？按这条规则，B200（sm_100）、RTX 5090（sm_120）、MI355X（gfx950，CDNA4）、RTX 4090（sm_89）和 MI300X（gfx942，CDNA3）各落在哪一类？</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：按目标三选一：有块缩放指令的走原生，scale 在指令内乘；没有的走软件换算，解码成 bf16、逐元素乘 scale、再做 bf16 矩阵乘；CDNA3 两侧都带 scale 时编译失败。
-• [T#B#sm_100]：tcgen05.mma 块缩放，scale 和累加器都在 TMEM，靠 5D 预排加 tcgen05.cp 送进去。
-• [T#B#sm_120]：mma.sync … block_scale，每个线程交一个 32 位寄存器的 scale、用 byte-id 选字节，累加器也在寄存器；FP8 × FP4 混合格式被拒，走软件换算。
-• [T#B#gfx950]：v_mfma_scale_f32_16x16x128_f8f6f4，scale 在 VGPR 里、用 op_sel 选字节，只认 E8M0，NVFP4 编译失败。
-• [T#B#sm_89]：软件换算加 bf16 的 mma.sync m16n8k16，只省显存不省算力；换算默认 scale 是 E8M0，NVFP4 编译失败。
-• [T#B#gfx942]：只登记了一侧带 scale 的模拟路径，两侧都带 scale 时报 Unsupported DotScaleOp；bf16 × MXFP4 用 upcast_mxfp 解码再做 bf16 MFMA。
-[T#B,!c47f17#边界]：只有一侧带 scale（比如 bf16 激活 × MXFP4 权重）时，所有目标都走软件换算，因为块缩放指令要求两侧都是 FP8、FP6 或 FP4。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：目标有块缩放指令、两侧都带 scale、格式受这条指令支持时走原生，scale 在指令内乘；否则走软件换算：解码成 bf16、逐元素乘 scale、再做 bf16 矩阵乘；CDNA3 的模拟路径只接一侧带 scale，两侧都带时编译失败。
+• [T#B#原生]：sm_100 的 tcgen05.mma，scale 和累加器都在 TMEM；sm_120 的块缩放 mma.sync，scale 和累加器都在寄存器；gfx950 的 scaled MFMA，scale 在 VGPR，只认 E8M0。
+• [T#B#软件换算]：sm_89 没有块缩放指令，解码后用 bf16 的 mma.sync，只省显存不省算力。
+• [T#B#编译失败]：gfx942 只登记了一侧带 scale 的模拟路径（比如 bf16 × MXFP4），两侧都带 scale 时报 Unsupported DotScaleOp。
+[T#B,!c47f17#边界]：“不走原生”有两种原因要分开：一侧根本不是低精度格式（如 bf16 × MXFP4）时，块缩放指令要求两侧都是 FP8、FP6 或 FP4，所有目标都走软件换算；一侧是 FP4 却不带 scale 时，sm_120 退回软件换算，是因为 Triton 3.7.1 的原生模式要求两侧都有 scale，不是指令本身的格式限制。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">原生三家都用 32 位装 4 个 scale；软件换算用 bf16；CDNA3 两侧失败</t>
+          <t xml:space="preserve">原生要指令、两侧 scale、格式三者都满足；否则软件换算；CDNA3 两侧带 scale 编译失败</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -327,22 +321,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 块缩放教程按 B200（sm_100）写：块 128 × 256，FP4 的 BLOCK_K = 256，4 级流水，4 个 warp。要在 RTX 5090（sm_120，每个 CTA 最多 101,376 字节共享内存，每个线程最多 255 个寄存器）上运行，要改什么？为什么？</t>
+          <t xml:space="preserve">Triton 3.7.1 的块缩放教程按 B200（sm_100）写：块 128 × 256，FP4 的 BLOCK_K = 256，4 级流水，4 个 warp。要在 RTX 5090（sm_120，每个 CTA 最多 101,376 字节共享内存，每个线程最多 255 个寄存器）上运行，要改什么？为什么？</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：原生指令照样有，但累加器从 TMEM 挪到了寄存器、共享内存也小了一半多，必须缩小分块，还要绕过入口检查。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：原生指令照样有，但累加器从 TMEM 挪到了寄存器、共享内存也小了一半多：要绕过入口检查，并按寄存器和共享内存的预算缩小分块。
 • [T#B#入口]：教程的 supports_block_scaling() 只放行 capability 10、11 和 gfx950，capability 12.0 的 5090 只打印提示就退出。
-• [T#B#寄存器]：128 × 256 的 FP32 累加器分给 4 个 warp，每个线程 256 个，已超过 255 个的上限；编译记录里用满 255 个并溢出。
-• [T#B#共享内存]：教程配置要 152,152 到 165,976 字节，放不下。
-• [T#B#可行配置]：128 × 128、3 级、8 个 warp：MXFP4 要 69,680 字节、199 个寄存器，累加器每线程 64 个，没有溢出。
-[T#B,!c47f17#边界]：NVFP4、MXFP4、MXFP8 在 sm_120 上都是原生指令，FP8 × FP4 混合走软件换算；教程的 5D scale 写法可以照用。</t>
+• [T#B#寄存器]：每个线程的累加器寄存器数 = BM·BN ÷ 线程数：128 × 256 的 FP32 累加器分给 4 个 warp（128 个线程），每个线程 256 个，已超过 255 个的上限，还没算别的寄存器。
+• [T#B#共享内存]：每级用量 × 级数要放进 101,376 字节：教程配置要 15 万字节以上，放不下。
+• [T#B#可行配置]：128 × 128、3 级、8 个 warp：累加器每线程 64 个，MXFP4 约用 7 万字节共享内存，没有溢出。
+[T#B,!c47f17#边界]：教程的 5D scale 写法在 sm_120 上可以照用。</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">入口检查；累加器进寄存器；128×128、3 级、8 个 warp</t>
+          <t xml:space="preserve">入口检查；BM·BN ÷ 线程数 对 255；每级 × 级数 对 101,376</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -359,16 +353,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先拿计算强度和平衡点比：平衡点约 247 FLOP/字节，即约 123 次乘加/字节；低于它受访存限制，高于它受计算限制。
-• [T#B#解码 M = 8]：受访存限制，B 读的字节约为 A 的 1/3.6，最多快约 3.6 倍；前提是解码跟得上带宽，这要用掉向量单元八到九成的吞吐。
-• [T#B#预填充 M = 4096]：受计算限制，B 少读的只是一小部分字节（激活和输出不变），换不来时间，B 最多和 A 一样快；只看解码能不能藏进 MFMA（约占 MFMA 时间的四成）：藏住时差不多，藏不住时 B 慢约四成。
-• [T#B#始终的好处]：显存容量：专家权重小约 3.8 倍。gpt-oss-120b 的 MLP 存 bf16 约 229 GB，超过单卡的 192 GB；存 MXFP4 约 61 GB。
-[T#B,!c47f17#边界]：强度要计入激活和输出的字节，单位要和平衡点一致；靠近平衡点时，结论对解码代价很敏感，要实测。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：解码（M = 8）时 B 最多快约 3.6 倍；预填充（M = 4096）时 B 最多和 A 持平，解码藏不住时慢约四成。依据是拿计算强度和平衡点（约 247 FLOP/字节，即约 123 次乘加/字节）比。
+• [T#B#解码 M = 8]：强度远低于平衡点，受访存限制：B 读的字节约为 A 的 1/3.6，最多快约 3.6 倍；前提是解码跟得上带宽，这要用掉向量单元约八成的吞吐。
+• [T#B#预填充 M = 4096]：受计算限制，B 少读的只是一小部分字节（激活和输出不变），换不来时间；只看解码能不能藏进 MFMA（约占 MFMA 时间的四成）：藏住时差不多，藏不住时 B 慢约四成。
+• [T#B#容量]：与负载无关，B 的权重小约 3.8 倍，省下的显存可以给 KV cache。
+[T#B,!c47f17#边界]：强度要计入激活、权重、scale 和输出的字节，单位要和平衡点一致；靠近平衡点时，结论对解码代价很敏感，要实测。</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">平衡点 123 次乘加/字节；解码看带宽、预填充看解码能否藏住；容量始终都有</t>
+          <t xml:space="preserve">解码最多快约 3.6 倍、预填充最多持平；平衡点 123 次乘加/字节；容量始终都有</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -386,10 +380,10 @@
       <c r="B15" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：先算每种资源单独把活干完要多久（t_mem、t_mfma、t_valu），再看它们能不能同时干：能同时干就取最长的一项，不能就相加。
-• [T#B#解码对 MFMA]：t_valu / t_mfma = (c ÷ P_valu) ÷ (BLOCK_M ÷ P_mfma) = 16c / BLOCK_M：c 是每解码一个 FP4、每个 lane 要执行几条向量指令，BLOCK_M 是一个解码出的 FP4 参与的乘加次数，16 = 653.7 ÷ 40.9。
+• [T#B#解码对 MFMA]：t_valu / t_mfma = (c ÷ P_valu) ÷ (BLOCK_M ÷ P_mfma) = 16c / BLOCK_M：P_valu 是向量单元每秒按 lane 计的指令数，P_mfma 是 MFMA 每秒的乘加数，16 = 653.7 ÷ 40.9；c 是每解码一个 FP4、每个 lane 要执行几条向量指令，BLOCK_M 是一个解码出的 FP4 参与的乘加次数。
 • [T#B#藏得住的门槛]：CDNA3 一条 16 个周期的 MFMA 发出 4 个周期后，才能同时发射向量指令，留出 12 个周期的空档，所以比值不超过约 0.75 才可能全部藏住。
 • [T#B#解码对带宽]：受访存限制、每个 FP4 只解码一次时，t_valu / t_mem = (c ÷ 40.9 万亿) ÷ (0.53125 ÷ 5.3 TB/s) ≈ 0.244c；要跟上 5.3 TB/s，c 不能超过约 4.1。
-• [T#B#c 从哪来]：从编出的代码里数：每个 wave 每个 K 步的非 MFMA 向量指令数 ÷ 每个 lane 解码的 FP4 数，例如 222 ÷ 64 ≈ 3.5。
+• [T#B#c 从哪来]：从能运行的配置编出的代码里数：每个 wave 每个 K 步的非 MFMA 向量指令数 ÷ 每个 lane 解码的 FP4 数，例如 MI300X 上 BLOCK_K = 128 的配置是 104 ÷ 32 ≈ 3.25；只编译不会检查 LDS 上限，先确认配置放得下。
 [T#B,!c47f17#边界]：峰值跑不满，能否真的并行要看调度和驻留的 wave 数；最终要用 rocprofiler-compute 之类的工具实测各资源的利用率。</t>
         </is>
       </c>
@@ -407,21 +401,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 的软件换算路径（FP4 解码成 bf16 再做矩阵乘）在 ttg.local_load 之后、按 dot 操作数的布局，在每个 warp（AMD 上叫 wave）自己的寄存器里解码。一个 CTA 的输出块由 warpsPerCTA 规定的若干 warp 分工计算。排法怎样影响“每个元素被解码几次、每一份参与几次乘加”？以 128 × 128 的 CTA 块、8 个 wave 排成 \[1, 8\] 和 \[2, 4\] 为例（写法是 \[M 方向的 wave 数, N 方向的 wave 数\]）。</t>
+          <t xml:space="preserve">在 Triton 3.7.1 的软件换算路径里（A 是 bf16 激活，B 是要解码成 bf16 的 FP4 权重），一个 CTA 的输出块由 warpsPerCTA 规定的若干 warp（AMD 上叫 wave）分工计算，写法是 \[M 方向的 wave 数, N 方向的 wave 数\]。以 AMD CDNA 上 128 × 128 的 CTA 块、8 个 wave 排成 \[1, 8\] 和 \[2, 4\] 为例，排法怎样影响每个权重元素被解码几次、每一份参与几次乘加？</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：每个 warp 只管自己的子块，只解码自己的 MMA 要用的那部分数据；warp 之间不共享寄存器，用到同一行 A 或同一列 B 的 warp 各解码一份。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：每个 wave 只算自己的子块，在自己的寄存器里存累加器、解码自己要用的那部分 B；wave 之间不共享寄存器，M 方向有几个 wave，同一列 B 就被解码几份。
 • [T#B#\[1, 8\]]：每个 wave 负责 128 行 × 16 列：每个 B 元素只被一个 wave 解码，参与 128 次乘加；但整块 A 每个 K 步要被读 8 遍。
 • [T#B#\[2, 4\]]：每个 wave 负责 64 行 × 32 列：A 少读一半，每个 B 元素被解码两次，每份只参与 64 次乘加，解码相对乘加的比例翻倍。
-• [T#B#谁定排法]：Triton 里写不了，由编译器决定：gfx942 的一侧模拟路径写死为 \[1, 8\]，gfx950 拆成“解码 + 普通矩阵乘”后按启发式排成 \[2, 4\]。
-[T#B,!c47f17#边界]：M 很小时 Triton 还会交换操作数（算 B·Aᵀ），这时每个 warp 的子块可能只有 16 行 B × 8 行 A，复用次数更低。</t>
+• [T#B#谁定排法]：Triton 里写不了，由编译器决定：Triton 3.7.1 中 gfx942 的一侧模拟路径写死为 \[1, 8\]，gfx950 拆成“解码 + 普通矩阵乘”后按启发式排成 \[2, 4\]。
+[T#B,!c47f17#边界]：这里只比较了解码次数和从 LDS 读取的量；CDNA3 的 LDS 带宽没有查到官方数字，两种排法没有折算成时间。</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">各 warp 解码自己的片段；排法决定复用次数；排法由编译器定</t>
+          <t xml:space="preserve">M 方向几个 wave 就解码几份；排法决定复用次数；排法由编译器定</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -433,16 +427,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton kernel 用指针读入 MXFP4 矩阵乘的操作数：A 是 \[M, K // 2\] 的 uint8（沿 K 两个 FP4 拼一个字节），它的 scale 是 \[M, K // 32\] 的 uint8；B 按 \[N, K // 2\] 存，scale 是 \[N, K // 32\]。packed 数据要不要在 kernel 里拆成两个元素？读取的偏移哪些要减半？B 和它的 scale 怎样传给 tl.dot_scaled？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 的 kernel 里用指针读入 MXFP4 矩阵乘的操作数：A 是 \[M, K // 2\] 的 uint8（沿 K 两个 FP4 拼一个字节），它的 scale 是 \[M, K // 32\] 的 uint8；B 按 \[N, K // 2\] 存，scale 是 \[N, K // 32\]。把这些交给 tl.dot_scaled 之前，packed 数据要不要在 kernel 里拆成两个元素？读取的偏移哪些要减半？</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不用拆：把打包的 uint8 块原样传给 tl.dot_scaled，格式写 "e2m1"；接口规定第一个元素在低 4 位。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不用拆：把打包的 uint8 块原样传给 tl.dot_scaled，格式写 "e2m1"（接口规定第一个元素在低 4 位）；偏移只有沿 K 的要从元素数换成字节数。
 • [T#B#拆包交给谁]：sm_120 的原生指令直接读打包的 FP4；sm_89 上编译器会自动插入 ttg.fp4_to_fp，在寄存器里拆开。
 • [T#B#偏移]：只有沿 K 的距离要从元素数换成字节数：uint8 指针加 1 就前进 1 个字节，也就是 2 个元素。所以 packed 每个 K 步前进 BLOCK_K // 2，scale 前进 BLOCK_K // 32；M、N 方向一行还是一行。
-• [T#B#B]：b 按 \[N, K // 2\] 读入后以 b.T 传入；rhs_scale 保持 \[N, K // 32\]，不要转置。
-[T#B,!c47f17#边界]：块宽（tl.arange 的长度）和前进量是两件事：块宽错了，编译时的形状检查会报错；前进量错了只会静默读错位置。</t>
+• [T#B#B 的传法]：b 按 \[N, K // 2\] 读入后以 b.T 传入；rhs_scale 保持 \[N, K // 32\]，不要转置。</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -485,21 +478,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">估算一个 kernel 的总时间：已知最忙的 SM 上发射指令要 t_issue，把最少要搬的字节搬完要 t_mem。两部分完全重叠和完全不重叠时，总时间各是多少？实际更可能靠近哪一端，由什么决定？以 RTX 5090 上 M = 16 的 W8A16 变式为例（bf16 激活 × MXFP8 权重）：t_issue ≈ 20.3 µs，t_mem ≈ 39.1 µs，每个 SM 同一时刻只驻留 1 个 CTA。</t>
+          <t xml:space="preserve">估算一个 kernel 的总时间：已知最忙的 SM 上发射指令要 t_issue，把最少要搬的字节搬完要 t_mem。两部分完全重叠时总时间是 max(t_issue, t_mem)，完全不重叠时是两者之和。实际更靠近哪一端，由什么决定？以 RTX 5090 上 M = 16 的 W8A16 变式为例（bf16 激活 × MXFP8 权重）：t_issue ≈ 20.3 µs，t_mem ≈ 39.1 µs，每个 SM 同一时刻只驻留 1 个 CTA。</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：完全重叠时总时间等于较长的一项 max(t_issue, t_mem)，完全不重叠时是两者之和；例子里是 39.1 到 59.4 µs，受显存限制。
-• [T#B#为什么取较长的]：两件事都必须做完，重叠最多只能把短的藏进长的里，就像两个线程并行跑完再 join；若取 20 µs，等于假设 70 MB 能在 20 µs 内搬完，需要约 3.5 TB/s 的带宽。
-• [T#B#靠近哪端]：看每个调度器上有几个 warp 轮流：只有 1 到 2 个时，一个 warp 等数据，没有别的 warp 能补上，实际靠近相加；M = 16 实测的软件路径就是这样（估计相加 44.7 µs，实测 45.1 µs）。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：看每个调度器上有几个 warp 能轮流：只有 1 到 2 个时，一个 warp 等数据，没有别的 warp 能补上，实际靠近相加。例子里每个 SM 只驻留 1 个 CTA，总时间在 39.1 到 59.4 µs 之间，更靠近 59.4 µs。
+• [T#B#实测印证]：M = 16 实测的软件路径也是这样：发射约 24.5 µs 加等数据 20.2 µs ≈ 44.7 µs，接近实测的 45.1 µs。
 • [T#B#换条件]：显存带宽翻倍后 t_mem ≈ 19.5 µs，较长的一项变成发射：下限 20.3 µs、上限 39.8 µs，受发射限制。
 [T#B,!c47f17#边界]：两项接近时，“受谁限制”只在完全重叠的前提下成立；重叠差时，两项都要缩短才明显见效。</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">下限取较长的一项、上限相加；warp 少则靠近相加</t>
+          <t xml:space="preserve">warp 少、驻留少则靠近相加；两项接近时谁限制要看重叠</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -537,17 +529,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">块缩放 FP4 里，若块内有一个约 8 倍的离群值、块 scale 对齐离群值，同块其余正常值都挤在块最大值的 1/8 以下，这时 E3M0 在这些正常值上比 E2M1 准。为什么“离群值毕竟是少数，所以仍选 E2M1”这句理由不完整？真实系统用哪些办法压低离群值的损失？</t>
+          <t xml:space="preserve">块缩放 FP4 里，若块内有一个约 8 倍的离群值、块 scale 对齐离群值，同块其余正常值都挤在块最大值的 1/8 以下，这时 E3M0 在这些正常值上比 E2M1 准。为什么“离群值毕竟是少数，所以仍选 E2M1”这句理由不完整？真实系统又怎样从块大小、量化前的变换和层的精度三方面压低离群值的损失？</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：还要看每个离群块损失多大：E2M1 在 1/8 以下只有 1/12 一个非零格点，离群块里误差大得多；离群值越大，需要的离群块占比越小，就能让结论反过来。
-• [T#B#量级]：8 倍离群值时，离群块约占 10%，E3M0 的总误差就开始小于 E2M1；20 倍时只要约 2% 到 3%。
-• [T#B#更小的块]：NVFP4 每 16 个一块，一个离群值只拖累 15 个数。
-• [T#B#旋转]：量化前乘一个随机 Hadamard 矩阵 H（元素是 ±1/4，各行两两正交），离群值被摊到 16 个数上；两个输入沿 K 乘同一个 H，因为 H·Hᵀ = I，乘积不变。NVIDIA 的 NVFP4 训练只在求权重梯度（Wgrad）的矩阵乘上用。
-• [T#B#高精度]：约 15% 的敏感线性层保持 BF16。
-[T#B,!c47f17#边界]：旋转也不是万能：每块都有 8 倍离群值的极端设定下，模拟的 32 点 Hadamard 只把 E2M1 的误差从 0.47 降到 0.37。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：还要看每个离群块损失多大：E2M1 在 1/8 以下只有 1/12 一个非零格点，离群块里误差大得多；8 倍离群值时，离群块约占 10% 就让 E3M0 的总误差反超，离群值越大，所需的占比越小。
+• [T#B#块大小]：块越小，一个离群值连累的数越少：NVFP4 每 16 个一块，只拖累 15 个数。
+• [T#B#旋转]：量化前乘一个 16 × 16 的随机 Hadamard 矩阵 H（元素是 ±1/4，各行两两正交），离群值被摊到 16 个数上；两个输入沿 K 乘同一个 H，因为 H·Hᵀ = I，乘积不变。
+• [T#B#层的精度]：对量化敏感的层保留 BF16。
+[T#B,!c47f17#边界]：10% 只是一个数量级，具体的反超点取决于数据分布。</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -590,61 +581,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">一个 CTA 负责 BM × BN 的输出块，沿 K 每 V 个元素一个 scale。在一个 scale 块上，“乘在部分和上”和“乘在元素上”各要乘几次 scale？比值 BM·BN / (V·(BM + BN)) 怎样理解？什么时候前者更省？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中、sm_100 上，若 scale 按逻辑二维存、能建起描述符（比如 NVFP4），kernel 不做 reshape、trans，直接把 \[128, BLOCK_K/V\] 的 scale 交给 tl.dot_scaled，scale 从 SMEM 进 TMEM 的路径会变成什么样？和教程的 5D 预排相比，多出来的代价在哪里？</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：乘在元素上，每个输入元素乘一次，共 V·(BM + BN) 次；乘在部分和上，每个部分和乘一次，共 BM·BN 次；后者除以前者就是这个比值。
-• [T#B#摊到乘加]：乘在元素上，每次乘加摊到 1/BM + 1/BN 次乘 scale（128 × 256 时约 1/85）；乘在部分和上摊到 1/V 次。所以 V 大于约 85 时后者更省。
-• [T#B#数值]：128 × 256 的块：V = 32 时比值约 2.7，V = 128 时约 0.67。
-[T#B,!c47f17#边界]：这里只数乘 scale：没算解码的成本，次数也不等于时间；而且乘在部分和上还要求 V ≥ 指令的 K。</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">分母数输入、分子数输出；1/BM + 1/BN 对 1/V</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · 节点 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sm_100 上，若 scale 按逻辑二维存、能建起描述符（比如 NVFP4），kernel 不做 reshape、trans，直接把 \[128, BLOCK_K/V\] 的 scale 交给 tl.dot_scaled，scale 从 SMEM 进 TMEM 的路径会变成什么样？和教程的 5D 预排相比，多出来的代价在哪里？</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：改走通用路径：所有 warp 用 ld.shared 把 scale 读进寄存器，再用 tcgen05.st 写进 TMEM；结果照样正确。
 • [T#B#寄存器]：寄存器里其实不重排字节：每个线程按地址取它那个 lane 要的 4 行，原样交给 tcgen05.st。
 • [T#B#代价]：每个 K 步所有 warp 都要参与搬 scale；每个 warp 都把整块 scale 写进自己的 32 个 lane，同一块读 4 遍；每条 tcgen05.st 之后要 tcgen05.wait::st 加 bar.sync，128 个线程到齐，才由一个线程发 MMA。
-• [T#B#对照]：教程的做法是一个线程发 12 条 tcgen05.cp（NVFP4，A 4 块、B 8 块），.warpx4 在拷贝时就写好 4 份副本，MMA 之前不用等。
+• [T#B#对照]：教程的做法是每个 K 步由一个线程发 12 条 tcgen05.cp（NVFP4，A 4 块、B 8 块），.warpx4 在拷贝时就写好 4 份副本，MMA 之前不用等。
 [T#B,!c47f17#边界]：TMA 请求也从连续的 2 KB 变成 128 段、每段 16 字节的小请求。</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t xml:space="preserve">全员 ld.shared + tcgen05.st；读 4 遍；两次全 CTA 等待</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · 节点 4</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t xml:space="preserve">块缩放教程的 scale 形状链：逻辑 \[M, K/V\] → 物理 (M/128, K/V/4, 32, 4, 4) → TMA 视图 (1, M/128, K/V/4, 2, 256) → kernel 里的 reshape、trans、reshape。怎样用“把下标拆成数位”的方法推导这串形状？哪些数字由硬件固定，哪些随分块、格式和输入大小变化？</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：把行号、列号按混合进制拆开：m = 128·mb + 32·g + r，j = 4·kc + c；reshape 只合并或拆分相邻的数位，不动字节；trans 改变数位的先后。
 • [T#B#块内]：(r, g, c) = (32, 4, 4) 由 TMEM 决定：32 个 lane，128 行折成 4 列，一个 32 位格子装 4 个 1 字节的 scale，都是硬件固定的。
@@ -653,9 +619,33 @@
 [T#B,!c47f17#边界]：整条链上唯一真正搬字节的，是主机端从逻辑矩阵排成物理顺序那一步：reshape 成 (mb, g, r, kc, c)，再 permute(0, 3, 2, 1, 4)。</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拆数位；reshape 不动字节；32/4/4 来自硬件、2×256 来自 TMA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · 节点 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton 3.7.1 的 sm_100 块缩放教程里，一块预排 scale 覆盖 128 行 × 4 个 scale（沿 K 共 4V 个元素）。BLOCK_K 的取值受哪些条件约束，往上加大时真正受什么限制？</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：定死的只是粒度：BLOCK_K = rep_k × 4V，而且要是一条 MMA 指令的 K 的整数倍（两种 FP4 格式是 64，MXFP8 是 32）；每个 K 步用几块（rep_k）可以自由选。
+• [T#B#TMEM]：不是瓶颈：一个 K 步的 scale 加上 FP32 累加器，也远没用满 TMEM 的 512 列。
+• [T#B#共享内存]：真正的限制是每级用量 × 流水级数：BLOCK_K 翻倍，每级用量也约翻倍，同样的共享内存只够一半的级数。</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">拆数位；reshape 不动字节；32/4/4 来自硬件、2×256 来自 TMA</t>
+          <t xml:space="preserve">rep_k × 4V、指令 K 的倍数；TMEM 不紧；共享内存 × 级数</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -667,87 +657,61 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">sm_100 的块缩放教程里，一块预排 scale 覆盖 128 行 × 4 个 scale（沿 K 共 4V 个元素）。BLOCK_K 是不是因此被 TMEM 和 V 定死了？它的取值受哪些条件约束？往上加大时真正受什么限制？</t>
+          <t xml:space="preserve">Triton 3.7.1 的块缩放教程为 MI355X（gfx950，CDNA4）另写了 shuffle_scales_cdna4。它和 NVIDIA sm_100 的 5D 预排，目标有什么不同？不预排会多付什么？</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：定死的只是粒度：BLOCK_K = rep_k × 4V，而且要是一条 MMA 指令的 K 的整数倍（两种 FP4 格式是 64，MXFP8 是 32）；每个 K 步用几块（rep_k）可以自由选。
-• [T#B#TMEM]：不是瓶颈：教程的 NVFP4 配置里，一个 K 步的 scale 只占 TMEM 512 列中的 48 列，128 × 256 的 FP32 累加器占 256 列。
-• [T#B#共享内存]：真正的限制是每级用量 × 流水级数：NVFP4 每级约 55 KB，4 级约 221 KB；BLOCK_K 翻倍到 512，同样的共享内存只够 2 级。
-• [T#B#对照]：DeepGEMM 在软件里每 128 个元素乘一次 scale，BLOCK_K 必须等于 scale 块，所以它断言 BLOCK_K == 128。
-[T#B,!c47f17#边界]：sm_120 每个 CTA 只有 101,376 字节共享内存，教程的配置在那里放不下。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：NVIDIA 的预排是让字节顺序等于 TMEM 的顺序，好让一条 tcgen05.cp 原样拷贝；AMD 的预排是让每个 lane 在 4 条 MFMA 里要用的 4 个 scale 在内存里挨着，一次 32 位读出。
+• [T#B#指令]：v_mfma_scale 的 64 个 lane 里，16 个沿 M 排、4 个沿 K 排，每个 lane 正好管 32 个 K 元素，也就是一个 scale；scale 放在一个 32 位 VGPR 里，用 op_sel 选字节。
+• [T#B#代价]：scale 按逻辑形状存时，从 LDS 读 scale 要逐字节读、再把字节拼起来；预排后每个 lane 一次 32 位读就拿到 4 个 scale；从显存读进 LDS 的指令两者相同。
+[T#B,!c47f17#边界]：和 NVIDIA 一样，预排只影响快慢，kernel 里会把它换回逻辑形状。</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">rep_k × 4V；TMEM 不紧；共享内存 × 级数</t>
+          <t xml:space="preserve">NV 对齐 TMEM；AMD 让每个 lane 的 4 个 scale 挨着</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · 节点 4</t>
+          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · 节点 5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 块缩放教程为 MI355X（gfx950，CDNA4）另写了 shuffle_scales_cdna4。它和 NVIDIA sm_100 的 5D 预排，目标有什么不同？不预排会多付什么？</t>
+          <t xml:space="preserve">PyTorch 里没有可以直接 .to() 过去的 MXFP4 类型。量化后已经得到落在 E2M1 格点上的浮点值（比如 3.0、−0.5），怎样把它们变成 4 位编码，并沿 K 把相邻两个编码打包进一个字节（第 j 个字节的低 4 位放第 2j 个元素）？</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：NVIDIA 的预排是让字节顺序等于 TMEM 的顺序，好让一条 tcgen05.cp 原样拷贝；AMD 的预排是让每个 lane 在 4 条 MFMA 里要用的 4 个 scale 在内存里挨着，一次 32 位读出。
-• [T#B#指令]：v_mfma_scale 的 64 个 lane 里，16 个沿 M 排、4 个沿 K 排，每个 lane 正好管 32 个 K 元素，也就是一个 scale；scale 放在一个 32 位 VGPR 里，用 op_sel 选字节。
-• [T#B#代价]：scale 按逻辑形状存时，从 LDS 读 scale 要 36 条逐字节的 ds_read_u8，还要拼字节；预排后只要 6 条 32 位读；从显存读进 LDS 的指令两者相同。
-[T#B,!c47f17#边界]：和 NVIDIA 一样，预排只影响快慢，kernel 里会把它换回逻辑形状。</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NV 对齐 TMEM；AMD 让每个 lane 的 4 个 scale 挨着</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · 节点 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PyTorch 里没有可以直接 .to() 过去的 MXFP4 类型。量化后已经得到落在 E2M1 格点上的浮点值（比如 3.0、−0.5），怎样把它们变成 4 位编码，并沿 K 把相邻两个编码打包进一个字节（第 j 个字节的低 4 位放第 2j 个元素）？</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：编码就是这个值在有序格点表 {0, 0.5, 1, 1.5, 2, 3, 4, 6} 里的下标，负数再加 8；打包是 byte = lo | (hi &lt;&lt; 4)。
 • [T#B#为什么是下标]：非负数的位模式当无符号整数比大小，顺序和数值一致，道理和 IEEE 浮点一样；符号是单独的最高位，所以 −3 是 13、−0.5 是 9、−0 是 8。
 • [T#B#整张量]：编码放在整数张量里，用步长为 2 的切片取出偶数列和奇数列：codes\[..., 0::2\] | (codes\[..., 1::2\] &lt;&lt; 4)。例：\[3.0, −0.5\] 的编码是 \[5, 9\]，打成 0x95。
-• [T#B#解包]：byte &amp; 0xF 是元素 2j，byte &gt;&gt; 4 是元素 2j+1，再交错放回；低 3 位查表，第 3 位定符号，最后乘 2^(scale 字节 − 127)。
+• [T#B#解包（延伸）]：byte &amp; 0xF 是元素 2j，byte &gt;&gt; 4 是元素 2j+1，再交错放回；低 3 位查表，最高位（bit 3）是符号位，整张量上用 torch.where(sign == 1, -v, v) 放回符号（分支改成两边都算、再按条件挑），最后乘 2^(scale 字节 − 127)。
 [T#B,!c47f17#边界]：浮点张量不能移位（左移对 Float 未实现），编码必须放在整数张量里，最后的 packed 是 uint8。</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t xml:space="preserve">值 → 下标 → 负数加 8；lo | (hi &lt;&lt; 4)；用整数张量</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · 练习 P1</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一个块缩放矩阵乘 kernel 在 RTX 5090 上数值测试全部通过。为什么这还不能说明它走了原生块缩放指令？要怎样检查？</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在 Triton 3.7.1 中，一个块缩放矩阵乘 kernel 编到 RTX 5090（sm_120）后数值测试全部通过。为什么这还不能说明它走了原生块缩放指令？要怎样检查？</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：原生指令和软件换算算出的结果都对，数值测试分不出两者；“结果对、但悄悄退回了软件换算”只能看编译产物。
 • [T#B#检查]：编到 sm_120 时，PTX 里要有 kind::mxf4nvf4.block_scale，TTGIR 里不能有 ttg.fp4_to_fp。
@@ -755,90 +719,92 @@
 [T#B,!c47f17#边界]：这类检查只编译、不运行，可以在没有 GPU 的机器上用替身驱动完成。</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数值分不出路径；PTX 有 block_scale、TTGIR 无 fp4_to_fp</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton 3.7.1 在没有原生块缩放指令可用时，把 tl.dot_scaled 拆成软件换算。以 RTX 5090 上的一条软件路径为例：A 是不带 scale 的 MXFP4，B 是带 scale 的 MXFP4。哪些操作数要做“解码”、哪些要做“scale 处理”，各由什么决定？其中哪一部分可以用 fast_math=True 省掉？</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：解码看存储格式：以 FP4 存放的操作数都要把 4 位码换成 bf16，与有没有 scale 无关；scale 处理看有没有 scale：只有带 scale 的操作数才乘 scale、做 NaN 处理。例子里 A、B 都要解码，只有 B 做 scale 处理。
+• [T#B#解码]：在 NVIDIA 上是 Triton 内联 PTX 的一次查表：prmt 按编码在两张字节表里挑出 bf16 的高、低字节，平均每个元素约 2 条指令。
+• [T#B#NaN 处理]：DecomposeScaledBlocked 逐元素做 where(scale == 0xFF, NaN, x)，因为把 scale 字节左移成 bf16 后，255 会变成 Inf 而不是 NaN；在 SASS 里就是 B 每个元素 1 条 SEL。
+• [T#B#fast_math]：fast_math=True 跳过 NaN 检查，这些 SEL 就没有了，在 M = 16 那次约占循环指令的 14%；代价是 scale 字节为 0xFF 时不再得到 NaN。
+• [T#B#W4A16]：A 改存 bf16 只去掉解码里较小、较便宜的一块（A 没有 scale 处理），按编译产物估算收益有限，没有实测。
+[T#B,!c47f17#边界]：只有能保证量化不会产生 0xFF 的 scale 时，才适合打开 fast_math。</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">数值分不出路径；PTX 有 block_scale、TTGIR 无 fp4_to_fp</t>
+          <t xml:space="preserve">解码看存储格式，scale 处理看有没有 scale；SEL 是 NaN 处理，fast_math 去掉它</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · A6</t>
+          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · M1 复查</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 没有原生块缩放指令可用时，把 tl.dot_scaled 拆成软件换算。哪些操作数需要“解码”、哪些需要“scale 处理”，各包含哪些工作？RTX 5090 上 M = 16 的实测软件路径（A 是不带 scale 的 MXFP4，B 是带 scale 的 MXFP4），每个 warp 每个 K 步的 1842 条指令怎样拆？tl.dot_scaled 的 fast_math=True 省掉什么？</t>
+          <t xml:space="preserve">在 MI300X（gfx942，CDNA3）上部署一个按 OCP E4M3（PyTorch 的 float8_e4m3fn）量化的 FP8 checkpoint：权重是 FP8 字节，另配权重 scale 和输入 scale。为什么不能把这些字节直接当成 MI300X 原生的 FP8 来用？要怎样转换（以 vLLM commit 8530aed 的 normalize_e4m3fn_to_e4m3fnuz 为例）？</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：以 FP4 存放的操作数都要解码（4 位码查表换成 bf16，与有没有 scale 无关）；只有带 scale 的操作数才做 scale 处理，即乘 scale 与 NaN 处理。
-• [T#B#拆分]：查表换算 816 条（A、B 全部 12,288 个元素）、重排与搬运约 433 条、B 的 NaN 处理 SEL 256 条（每个 B 元素 1 条）、乘 scale 的 HMUL2 128 条（每条乘两个 bf16）、其他 209 条。
-• [T#B#NaN 处理]：DecomposeScaledBlocked 逐元素做 where(scale == 0xFF, NaN, x)，因为把 scale 字节左移成 bf16 后，255 会变成 Inf 而不是 NaN。
-• [T#B#fast_math]：fast_math=True 时跳过 NaN 检查，这 256 条 SEL 就没有了，约占循环的 14%；代价是 scale 字节为 0xFF 时不再得到 NaN。
-[T#B,!c47f17#边界]：只有能保证量化不会产生 0xFF 的 scale 时，才适合打开 fast_math。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：MI300X 原生的 FP8 是 FNUZ 变体：bias 是 8 而不是 7，同样的位表示的值正好是 OCP E4M3 的一半，而且 0x80 在 OCP 里是 −0，在 FNUZ 里是 NaN。直接复用字节，反量化的值整体小一半，原来的 −0 变成 NaN。
+• [T#B#格式差别]：FNUZ 没有 −0 和 Inf，0x80 是唯一的 NaN，最大值 240（OCP E4M3 是 448）；比如字节 0x7E 在 OCP 里是 448，在 FNUZ 里是 224。
+• [T#B#转换]：vLLM 做三步：把字节 0x80 改成 0；把同样的位按 FNUZ 重新解读；把权重 scale 和输入 scale 都乘 2。同样的位在 FNUZ 里只有一半大，scale 翻倍后反量化的结果不变。
+[T#B,!c47f17#边界]：这是 CDNA3 的问题：MI350 系列（CDNA4）改用了 OCP 格式，不需要这一步；换到别的加速器时，先查清它原生的 FP8 是哪一种变体。</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">解码看存储格式，scale 处理看有没有 scale；SEL 是 NaN 处理</t>
+          <t xml:space="preserve">FNUZ：bias 8、同位值减半、0x80 是 NaN；0x80 → 0、按 FNUZ 解读、scale × 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · M1 复查</t>
+          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · 节点 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 的 Fp4ToFpOpToLLVM 用一段内联 PTX，把一个 32 位寄存器里的 8 个 FP4（E2M1）编码转成 8 个 bf16。它是怎样做的？每个元素平均约几条指令？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 里给 NVIDIA 的 TMA 建描述符：一块 scale 是 16 行 × 16 个字节，这 16 行在显存里首尾相接（行距正好 16 字节）。想在描述符里把它们表示成一段连续的 256 字节，而不是 16 段 16 字节，该怎样表达？</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：做一次查表：E2M1 编码的低 3 位是有序格点的下标，用 prmt（相当于 CUDA 的 __byte_perm：从两个 32 位寄存器拼成的 8 个字节里，按选择器的每个半字节挑一个字节）分别查 bf16 的低字节表和高字节表。
-• [T#B#步骤]：先用 &amp; 0x77777777 去掉符号位得到下标，用 &amp; 0x88888888 再右移 3 位取出符号；查低字节表（0xC0800000、0xC0804000）和高字节表（0x3F3F3F00、0x40404040），负数在高字节补 0x80；后 4 个编码右移 16 位再查一遍，最后 4 条 prmt 把低、高字节交错拼成 4 个 bf16x2。
-• [T#B#条数]：共 2 条 and、3 条 shr、10 条 prmt、2 条 or，17 条处理 8 个元素，平均每个元素约 2.1 条。
-[T#B,!c47f17#边界]：先清掉符号位还有一个原因：prmt 选择器半字节的最高位另有含义，表示把所选字节的符号位复制满整个字节。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：没有单独的“连续”声明，形状和步长本身就是声明：把首尾相接的几行在形状里合成一维，比如 \[16, 16\] 写成 \[256\]，在主机端先把张量 reshape 成合并后的形状，再建描述符。
+• [T#B#合并条件]：描述符只认“地址 = 起点 + Σ 下标 × 步长”：相邻两维能合并，当且仅当外层步长 = 内层大小 × 内层步长，也就是两维首尾相接。
+• [T#B#Triton]：TensorDescriptor.from_tensor 按张量原有的形状和步长建描述符，不会替你合并。
+• [T#B#swizzle]：“最内维尽量拉到 256”只对不做 swizzle 的描述符成立：开了 swizzle 时，块的最内维不能超过 swizzle 宽度。
+[T#B,!c47f17#边界]：TMA 硬件内部会不会把首尾相接的短行拼成大消息，NVIDIA 没有公开；“最内维越大、消息越大”只出自教程注释，没有测量过。</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">两张字节表加符号；17 条处理 8 个元素</t>
+          <t xml:space="preserve">形状和步长就是声明；外层步长 = 内层大小 × 内层步长；swizzle 限制最内维</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · M1 复查</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RTX 5090 上 M = 16、N = K = 8192 的软件换算路径（A、B 都是 MXFP4，A 不带 scale）实测 45.1 µs。若把 A 改存 bf16（W4A16，只有 B 要解码），按编译出的 SASS 估算能快多少？为什么去掉 A 的解码收益不大？</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：本机编译每个 warp 每个 K 步 1608 条（原来 1842 条），发射约 21.4 µs，显存约 20.3 µs，两项几乎一样长；按两项相加估约 41.7 µs，只快约 7%。
-• [T#B#原因]：A 只占每个 warp 每个 K 步解码的 12,288 个元素里的 4096 个，又没有 scale 处理，只要查表那约 2.1 条/元素；B 每个元素约 5.4 条（含 NaN 处理与乘 scale），一点没少。
-• [T#B#副作用]：A 改成 bf16 后，读共享内存的指令从 19 条增加到 35 条。
-[T#B,!c47f17#边界]：两项接近时，模型里一点小误差就会让“谁是限制”翻过来（按题设估是显存略长，按实际编译是发射略长），更稳妥的说法是“两者相当”；这些只是编译估算，没有实测。</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1608 对 1842 条；21.4 对 20.3 µs；A 是解码里小而便宜的一块</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · M1 复查</t>
+          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · 节点 4</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-10-block-scaled-matmul-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-10-block-scaled-matmul-technical-qa.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -300,16 +300,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：目标有块缩放指令、两侧都带 scale、格式受这条指令支持时走原生，scale 在指令内乘；否则走软件换算：解码成 bf16、逐元素乘 scale、再做 bf16 矩阵乘；CDNA3 的模拟路径只接一侧带 scale，两侧都带时编译失败。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：目标有块缩放指令、两侧的元素与 scale 格式都受这条指令支持，并满足 Triton 3.7.1 原生模式的额外要求（如 sm_120 要求两侧都带 scale）时走原生，scale 在指令内乘；否则走软件换算：解码成 bf16、逐元素乘 scale、再做 bf16 矩阵乘；CDNA3 的模拟路径只接一侧带 scale，两侧都带时编译失败。
 • [T#B#原生]：sm_100 的 tcgen05.mma，scale 和累加器都在 TMEM；sm_120 的块缩放 mma.sync，scale 和累加器都在寄存器；gfx950 的 scaled MFMA，scale 在 VGPR，只认 E8M0。
 • [T#B#软件换算]：sm_89 没有块缩放指令，解码后用 bf16 的 mma.sync，只省显存不省算力。
 • [T#B#编译失败]：gfx942 只登记了一侧带 scale 的模拟路径（比如 bf16 × MXFP4），两侧都带 scale 时报 Unsupported DotScaleOp。
-[T#B,!c47f17#边界]：“不走原生”有两种原因要分开：一侧根本不是低精度格式（如 bf16 × MXFP4）时，块缩放指令要求两侧都是 FP8、FP6 或 FP4，所有目标都走软件换算；一侧是 FP4 却不带 scale 时，sm_120 退回软件换算，是因为 Triton 3.7.1 的原生模式要求两侧都有 scale，不是指令本身的格式限制。</t>
+[T#B,!c47f17#边界]：“不走原生”有两种原因要分开：一侧根本不是低精度格式（如 bf16 × MXFP4）时，块缩放指令要求两侧都是 FP8、FP6 或 FP4，所有目标都走软件换算；一侧是 FP4 却不带 scale 时，sm_120 退回软件换算，是因为 Triton 3.7.1 的 sm_120 原生模式要求两侧都有 scale，不是指令本身的格式限制。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">原生要指令、两侧 scale、格式三者都满足；否则软件换算；CDNA3 两侧带 scale 编译失败</t>
+          <t xml:space="preserve">原生要有指令、格式受支持、过得了原生模式的额外要求；否则软件换算；CDNA3 两侧带 scale 编译失败</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -808,6 +808,32 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在 Triton 3.7.1 中，把 NVFP4 × NVFP4（E2M1 元素，每 16 个元素配一个 UE4M3 块 scale）的 tl.dot_scaled 分别编到 RTX 4090（sm_89，没有块缩放指令）和 MI355X（gfx950，CDNA4，有缩放 MFMA），各会怎样？为什么？</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：两处都编译失败。RTX 4090 只能走软件换算，而它把 scale 字节直接移位成 bf16 的指数，只适用于只有指数的 E8M0；MI355X 的缩放 MFMA 只接 E8M0、每 32 个元素一个 scale，Triton 3.7.1 的退路在那里也没接住 NVFP4。
+• [T#B#RTX 4090]：软件换算先把元素解码成 bf16，再把 E8M0 的 scale 字节零扩展、左移 7 位，正好落进 bf16 的 8 位指数段（两者 bias 都是 127），一次移位、没有误差，然后逐元素相乘、交给 bf16 的 mma.sync。这一步默认 scale 只有指数，UE4M3 带 3 位尾数，套不上，编译时断言失败；H100（sm_90）上也一样。
+• [T#B#MI355X]：v_mfma_scale 的 64 个 lane 里，每个 lane 正好管 32 个 K 元素、对应一个 E8M0 scale；NVFP4 的 scale 类型和块大小都对不上，走不了原生。CDNA4 也登记了“解码 + 普通矩阵乘”的退路，但在 Triton 3.7.1 里它也没接住 NVFP4，编译报错。
+• [T#B#对照]：同样两个目标上，MXFP4 在 RTX 4090 走软件换算、在 MI355X 走原生；在这次编译探测的目标里，NVFP4 只有 B200（sm_100）和 RTX 5090（sm_120）编得过。所以在 Triton 3.7.1 里选 NVFP4，就只能面向 Blackwell。
+[T#B,!c47f17#边界]：换成 MXFP4 也不是哪里都能编：MI300X（gfx942）上 Triton 3.7.1 只模拟一侧带 scale，MXFP4 × MXFP4 同样编译失败。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">软件换算靠 E8M0 移位进 bf16 指数；缩放 MFMA 只认 E8M0、每 32 个一个；NVFP4 只在 Blackwell 上编得过</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">块缩放矩阵乘学习记录 10-20 · 节点 5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>